--- a/考核材料/小组材料/成员任务表.xlsx
+++ b/考核材料/小组材料/成员任务表.xlsx
@@ -10,7 +10,7 @@
     <sheet name="成员任务" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'成员任务'!$A$2:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'成员任务'!$A$2:$J$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1232,8 +1232,284 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>需求与设计</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>数据库设计：ER图、数据字典与迁移脚本梳理</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>付智康</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>开发</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>ER图、数据字典、迁移清单</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>42个Flyway迁移脚本整理归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>开发-迭代1</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>账号与安全：密码找回、登录限流与安全事件</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>付智康</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>开发</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>46293</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>账号安全模块</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>验证码/限流/安全事件记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>开发-迭代2</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>通知中心：站内通知与通知偏好</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>付智康</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>开发</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>46306</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>通知模块</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>未读/已读状态与邮件降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>开发-迭代2</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>前端页面：候选人工作台与企业端页面</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>杨旺鑫</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>46306</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>前端页面</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>工作台/企业招聘页/登录注册</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>接口联调测试与权限校验</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>杨旺鑫</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>46307</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>接口测试记录</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>后端接口与角色权限边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>功能回归测试</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>杨旺鑫</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>46307</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>回归测试记录</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>协助武心怡做核心链路回归</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:J17"/>
+  <autoFilter ref="A2:J23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>

--- a/考核材料/小组材料/成员任务表.xlsx
+++ b/考核材料/小组材料/成员任务表.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="成员任务" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="7天计划" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'成员任务'!$A$2:$J$23</definedName>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +39,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,8 +61,13 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -79,11 +89,44 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,6 +146,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1520,4 +1571,834 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>成员</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>天数</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>计划任务</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>任务完成情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>张嘉豪（组长）</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Day1</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>需求分析与总体架构设计</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>确定2感知模块+1扩展能力选题</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Day2</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>数据库与接口设计评审</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>评审通过，ER图定稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Day3</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>业务闭环：登录与预约开发</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>登录预约走通</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Day4</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>角色查询与存储联动</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>数据真实联动正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Day5</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Docker编排与网关配置</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>6服务一键启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Day6</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>健康检查与联调</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>全部服务Healthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Day7</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>README与小组报告汇总</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>定稿与现场一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>高弨（核心功能）</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Day1</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>语音分析服务框架搭建</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>FastAPI骨架完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Day2</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>语速与流利度算法实现</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>四维分析初版完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Day3</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>情绪清晰度+ffmpeg兜底</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>webm转码正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Day4</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Java接入与评分融合</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>旁路增强跑通</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Day5</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>文本理解评价证据层</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>text_evidence落库</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Day6</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>报告可追溯接口</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>逐题返回正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Day7</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>联调与性能优化</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>全链路验证通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>乔佳琪（简历与题目）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Day1</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>简历解析模块设计</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>解析方案确定</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Day2</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>技能画像提取</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>画像生成正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Day3</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>智能组卷加权选题</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>组卷功能跑通</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Day4</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>组卷记录持久化</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>题目来源可查</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Day5</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>配置模板占位符化</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>密钥不落仓库</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Day6</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>部署脚本与联调</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>一键部署成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Day7</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>企业端越权测试</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>拦截生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>武心怡（前端/测试）</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Day1</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>面试大厅页面开发</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>表单校验完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Day2</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>作答交互与状态处理</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>加载错误态齐全</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Day3</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>报告页语音区块</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>逐题展示完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Day4</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>文本评价区块</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>未评估显示正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Day5</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>测试用例设计</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>15条用例完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Day6</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>异常与权限测试执行</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>403可复现</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Day7</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>项目风险分析</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>5条风险清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>付智康（数据库/安全）</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Day1</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>ER图与数据字典</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>完成定稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Day2</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Flyway迁移脚本梳理</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>V1-V49归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Day3</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>验证码与登录限流</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>限流生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Day4</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>密码找回重置票据</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>流程走通</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Day5</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>账号安全事件记录</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>落库可查</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Day6</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>站内通知未读已读</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>通知正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Day7</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>邮件降级与通知偏好</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>失败不误报</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>杨旺鑫（前端/测试）</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Day1</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>候选人工作台页面</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>数据源独立降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Day2</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>企业端招聘页面</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>岗位申请页完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Day3</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>登录注册忘记密码</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>校验完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Day4</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>接口联调测试</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>返回正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Day5</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>角色权限校验</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>越权403拦截</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Day6</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>核心链路回归</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>回归通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Day7</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>回归记录汇总归档</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>与测试表一致</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A30:A36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>